--- a/inst/apps/LowerBoiseBCGCalc/external/RMD/files/Requirements.xlsx
+++ b/inst/apps/LowerBoiseBCGCalc/external/RMD/files/Requirements.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/GreatPlainsBCGCalc/inst/apps/GreatPlainsBCGCalc/external/RMD/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/LowerBoiseBCGCalc/inst/apps/LowerBoiseBCGCalc/external/RMD/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2397B59E-CFC2-4FC1-9863-5185E4ABE346}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCAC4D5B-EE88-4EB3-BDC8-6B60F083D2C8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Req_metadata" sheetId="1" r:id="rId1"/>
     <sheet name="Fish_classes" sheetId="2" r:id="rId2"/>
     <sheet name="Bug_classes" sheetId="3" r:id="rId3"/>
+    <sheet name="Req_fields" sheetId="4" r:id="rId4"/>
+    <sheet name="Opt_Fields" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="70">
   <si>
     <t>Index_Name</t>
   </si>
@@ -183,13 +185,67 @@
   </si>
   <si>
     <t>Number of individuals</t>
+  </si>
+  <si>
+    <t>Fish</t>
+  </si>
+  <si>
+    <t>Bugs</t>
+  </si>
+  <si>
+    <t>Allowable entries</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Unique sample identifier</t>
+  </si>
+  <si>
+    <t>Taxon name</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>non-negative real numbers; should not be blank</t>
+  </si>
+  <si>
+    <t>see list below (must match exactly)</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>non-negative real numbers; blanks are OK</t>
+  </si>
+  <si>
+    <t>Length, units = mm</t>
+  </si>
+  <si>
+    <t>Column Heading Name</t>
+  </si>
+  <si>
+    <t>N_Anomalies</t>
+  </si>
+  <si>
+    <t>must match exactly</t>
+  </si>
+  <si>
+    <t>number of individuals with Deformity, Erosion, Lesion or Tumor (DELT) anomalies</t>
+  </si>
+  <si>
+    <t>Density_m2</t>
+  </si>
+  <si>
+    <t>number of individuals per meter squared (count x subsample correction factor x area correction factor)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,8 +267,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -228,6 +297,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -259,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -272,6 +347,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -851,4 +944,224 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFB8AC2-01F5-4B2A-9796-21A667189916}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139E60C5-FE55-4EFC-AF95-3F57B2FCD1FC}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="94.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inst/apps/LowerBoiseBCGCalc/external/RMD/files/Requirements.xlsx
+++ b/inst/apps/LowerBoiseBCGCalc/external/RMD/files/Requirements.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/LowerBoiseBCGCalc/inst/apps/LowerBoiseBCGCalc/external/RMD/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{512F813A-223E-4250-B112-E4A9FDD03CC0}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_F25DC773A252ABDACC1048C1615860685BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB01E6B7-C639-40E6-BF5F-B9CC3EFEA2DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="40">
   <si>
     <t>Description</t>
   </si>
@@ -37,9 +37,6 @@
     <t>Data Type</t>
   </si>
   <si>
-    <t>flexible</t>
-  </si>
-  <si>
     <t>text</t>
   </si>
   <si>
@@ -82,12 +79,6 @@
     <t>Count</t>
   </si>
   <si>
-    <t>non-negative real numbers; should not be blank</t>
-  </si>
-  <si>
-    <t>see list below (must match exactly)</t>
-  </si>
-  <si>
     <t>Length</t>
   </si>
   <si>
@@ -113,6 +104,48 @@
   </si>
   <si>
     <t>number of individuals per meter squared (count x subsample correction factor x area correction factor)</t>
+  </si>
+  <si>
+    <t>locationId</t>
+  </si>
+  <si>
+    <t>text or numeric</t>
+  </si>
+  <si>
+    <t>activityYear</t>
+  </si>
+  <si>
+    <t>activityDate</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>Site identifier</t>
+  </si>
+  <si>
+    <t>Year of the sampling event</t>
+  </si>
+  <si>
+    <t>Example: 10/26/1996. Not required for fish because the two passes are sometimes done on different dates.</t>
+  </si>
+  <si>
+    <t>Flexible</t>
+  </si>
+  <si>
+    <t>Positive integer</t>
+  </si>
+  <si>
+    <t>Date, preferably in this format: MM/DD/YYYY</t>
+  </si>
+  <si>
+    <t>Non-negative real numbers; should not be blank</t>
+  </si>
+  <si>
+    <t>See list below (must match exactly)</t>
+  </si>
+  <si>
+    <t>Non-negative real numbers; blanks are OK</t>
   </si>
 </sst>
 </file>
@@ -467,15 +500,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFB8AC2-01F5-4B2A-9796-21A667189916}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="97.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -483,117 +516,175 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
+      <c r="A2" t="s">
+        <v>26</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>10</v>
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="5"/>
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -620,19 +711,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -640,44 +731,44 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
